--- a/templates/swipe_data_template.xlsx
+++ b/templates/swipe_data_template.xlsx
@@ -14,7 +14,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="60">
+  <si>
+    <t>S.No</t>
+  </si>
+  <si>
+    <t>Employee Name</t>
+  </si>
   <si>
     <t>Employee ID</t>
   </si>
@@ -25,49 +31,169 @@
     <t>Weekday</t>
   </si>
   <si>
+    <t>Shift Code</t>
+  </si>
+  <si>
     <t>Login</t>
   </si>
   <si>
     <t>Logout</t>
   </si>
   <si>
+    <t>Extra Work Hours</t>
+  </si>
+  <si>
     <t>Total Working Hours</t>
   </si>
   <si>
     <t>Attendance Status</t>
   </si>
   <si>
-    <t>EMP001</t>
-  </si>
-  <si>
-    <t>EMP002</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
+    <t>Floor Unit</t>
+  </si>
+  <si>
+    <t>Business Unit</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Sub-Department</t>
+  </si>
+  <si>
+    <t>Otsox</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>01/07/2025</t>
+  </si>
+  <si>
+    <t>02/07/2025</t>
+  </si>
+  <si>
+    <t>03/07/2025</t>
+  </si>
+  <si>
+    <t>04/07/2025</t>
+  </si>
+  <si>
+    <t>05/07/2025</t>
+  </si>
+  <si>
+    <t>06/07/2025</t>
+  </si>
+  <si>
+    <t>07/07/2025</t>
+  </si>
+  <si>
+    <t>08/07/2025</t>
+  </si>
+  <si>
+    <t>09/07/2025</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>Friday</t>
   </si>
   <si>
     <t>Saturday</t>
   </si>
   <si>
-    <t>09:00:00</t>
-  </si>
-  <si>
-    <t>09:15:00</t>
-  </si>
-  <si>
-    <t>18:00:00</t>
-  </si>
-  <si>
-    <t>18:30:00</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>08:15</t>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>10:32</t>
+  </si>
+  <si>
+    <t>10:29</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>10:49</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>17:46</t>
+  </si>
+  <si>
+    <t>17:41</t>
+  </si>
+  <si>
+    <t>17:52</t>
+  </si>
+  <si>
+    <t>17:42</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>00:48</t>
+  </si>
+  <si>
+    <t>00:41</t>
+  </si>
+  <si>
+    <t>00:52</t>
+  </si>
+  <si>
+    <t>00:42</t>
+  </si>
+  <si>
+    <t>06:53</t>
+  </si>
+  <si>
+    <t>07:17</t>
+  </si>
+  <si>
+    <t>07:21</t>
+  </si>
+  <si>
+    <t>07:12</t>
+  </si>
+  <si>
+    <t>AA</t>
   </si>
   <si>
     <t>AP</t>
+  </si>
+  <si>
+    <t>BL-A-5F</t>
+  </si>
+  <si>
+    <t>WCS</t>
+  </si>
+  <si>
+    <t>WCS/MSE7</t>
+  </si>
+  <si>
+    <t>WS1</t>
   </si>
 </sst>
 </file>
@@ -425,10 +551,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -450,51 +576,452 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
+    <row r="2" spans="1:15">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M2" t="s">
+        <v>57</v>
+      </c>
+      <c r="N2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" t="s">
+        <v>54</v>
+      </c>
+      <c r="L3" t="s">
+        <v>56</v>
+      </c>
+      <c r="M3" t="s">
+        <v>57</v>
+      </c>
+      <c r="N3" t="s">
+        <v>58</v>
+      </c>
+      <c r="O3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" t="s">
+        <v>55</v>
+      </c>
+      <c r="L4" t="s">
+        <v>56</v>
+      </c>
+      <c r="M4" t="s">
+        <v>57</v>
+      </c>
+      <c r="N4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L5" t="s">
+        <v>56</v>
+      </c>
+      <c r="M5" t="s">
+        <v>57</v>
+      </c>
+      <c r="N5" t="s">
+        <v>58</v>
+      </c>
+      <c r="O5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N6" t="s">
+        <v>58</v>
+      </c>
+      <c r="O6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" t="s">
+        <v>52</v>
+      </c>
+      <c r="K8" t="s">
+        <v>55</v>
+      </c>
+      <c r="L8" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" t="s">
+        <v>58</v>
+      </c>
+      <c r="O8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" t="s">
+        <v>57</v>
+      </c>
+      <c r="N9" t="s">
+        <v>58</v>
+      </c>
+      <c r="O9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="C10" t="s">
         <v>16</v>
       </c>
-      <c r="G3" t="s">
-        <v>17</v>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O10" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
